--- a/01.Basic Formulas.xlsx
+++ b/01.Basic Formulas.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Science\Data Science\2.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F40E22A-0705-4133-9CDD-CFDEC62260FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91C60DD0-7D74-4E92-9608-9026AB80A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5330D8FD-06D4-4B36-9FA2-5302D6A217B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5330D8FD-06D4-4B36-9FA2-5302D6A217B1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Student Weight" sheetId="1" r:id="rId1"/>
+    <sheet name="Items Price" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Greg      </t>
   </si>
@@ -77,13 +78,70 @@
   <si>
     <t xml:space="preserve">4) The average of Greg's, Richards &amp; Denvers weight
 </t>
+  </si>
+  <si>
+    <t>Item Spreadsheet</t>
+  </si>
+  <si>
+    <t>Sl No.</t>
+  </si>
+  <si>
+    <t>Name of Item</t>
+  </si>
+  <si>
+    <t>Cost of Each Item</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Price (Cost + Shipping)</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Canon Powershot A560</t>
+  </si>
+  <si>
+    <t>Nokia 6288</t>
+  </si>
+  <si>
+    <t>PS3</t>
+  </si>
+  <si>
+    <t>Compaq Presario C714NR</t>
+  </si>
+  <si>
+    <t>Apple Ipod Nano</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Tax @ 4.5%</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Money Left over</t>
+  </si>
+  <si>
+    <t>Total Amount = 160000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\₹#,##0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +173,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,8 +218,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -165,22 +260,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,17 +704,17 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="4">
         <f>SUM(B6,B8)</f>
         <v>109</v>
       </c>
@@ -587,7 +723,7 @@
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="4">
         <f>B7-B10</f>
         <v>-3</v>
       </c>
@@ -596,20 +732,20 @@
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="4">
         <f>SUM(B5:B11)</f>
         <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="G29" s="6">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="4">
         <f>AVERAGE(B5,B11,B9)</f>
         <v>65.333333333333329</v>
       </c>
@@ -622,4 +758,248 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE13BFB1-FFC1-4AF4-955E-F9EBF747F32F}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="10">
+        <v>6649</v>
+      </c>
+      <c r="D4" s="10">
+        <v>600</v>
+      </c>
+      <c r="E4" s="10">
+        <f>D4+C4</f>
+        <v>7249</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10">
+        <f>E4*F4</f>
+        <v>21747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="10">
+        <v>9999</v>
+      </c>
+      <c r="D5" s="10">
+        <v>350</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" ref="E5:E8" si="0">D5+C5</f>
+        <v>10349</v>
+      </c>
+      <c r="F5" s="9">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <f>E5*F5</f>
+        <v>41396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10">
+        <v>25499</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1150</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" si="0"/>
+        <v>26649</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <f>E6*F6</f>
+        <v>26649</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="10">
+        <v>29999</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1500</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>31499</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <f>E7*F7</f>
+        <v>31499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5899</v>
+      </c>
+      <c r="D8" s="10">
+        <v>450</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>6349</v>
+      </c>
+      <c r="F8" s="9">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <f>F8*E8</f>
+        <v>31745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="10">
+        <f>SUM(G4:G8)</f>
+        <v>153036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="10">
+        <f>G9*0.045</f>
+        <v>6886.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="10">
+        <f>G9+G10</f>
+        <v>159922.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="10">
+        <f>160000-G11</f>
+        <v>77.380000000004657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C15:D15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>